--- a/data/trans_orig/MCS12_SP-Edad-trans_orig.xlsx
+++ b/data/trans_orig/MCS12_SP-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media del componente de salud mental (SF12)</t>
+          <t>Puntuación media del componente de salud mental (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53,66; 54,59</t>
+          <t>53,68; 54,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53,54; 54,54</t>
+          <t>53,5; 54,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53,88; 54,96</t>
+          <t>53,84; 54,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54,18; 56,02</t>
+          <t>54,18; 56,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>51,98; 53,2</t>
+          <t>51,98; 53,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,82; 53,29</t>
+          <t>51,75; 53,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,76; 54,05</t>
+          <t>52,74; 54,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>50,92; 53,69</t>
+          <t>50,91; 53,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53,01; 53,76</t>
+          <t>53,01; 53,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52,81; 53,79</t>
+          <t>52,86; 53,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53,53; 54,37</t>
+          <t>53,55; 54,37</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,21; 54,81</t>
+          <t>53,17; 54,86</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>53,09; 53,97</t>
+          <t>53,08; 53,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52,5; 53,55</t>
+          <t>52,54; 53,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52,29; 53,38</t>
+          <t>52,22; 53,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52,88; 54,81</t>
+          <t>52,75; 54,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,53; 51,92</t>
+          <t>50,5; 51,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,6; 51,99</t>
+          <t>50,63; 52,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,05; 53,26</t>
+          <t>51,96; 53,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>51,63; 53,26</t>
+          <t>51,54; 53,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>52,09; 52,89</t>
+          <t>52,1; 52,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51,82; 52,7</t>
+          <t>51,86; 52,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52,38; 53,16</t>
+          <t>52,34; 53,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52,5; 53,71</t>
+          <t>52,52; 53,74</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51,71; 52,84</t>
+          <t>51,67; 52,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51,3; 52,57</t>
+          <t>51,31; 52,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52,1; 53,16</t>
+          <t>52,1; 53,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52,22; 53,69</t>
+          <t>52,13; 53,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50,36; 51,57</t>
+          <t>50,35; 51,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,57; 50,12</t>
+          <t>48,59; 50,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,24; 52,53</t>
+          <t>51,28; 52,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51,93; 52,96</t>
+          <t>51,9; 52,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>51,19; 52,03</t>
+          <t>51,19; 51,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50,16; 51,13</t>
+          <t>50,14; 51,17</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51,91; 52,75</t>
+          <t>51,8; 52,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>52,24; 53,21</t>
+          <t>52,2; 53,16</t>
         </is>
       </c>
     </row>
@@ -1136,52 +1136,52 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>51,74; 53,0</t>
+          <t>51,78; 53,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50,97; 52,38</t>
+          <t>51,0; 52,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50,86; 52,22</t>
+          <t>50,81; 52,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51,93; 54,27</t>
+          <t>52,01; 54,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,12; 50,64</t>
+          <t>49,0; 50,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,63; 49,35</t>
+          <t>47,72; 49,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,44; 50,89</t>
+          <t>49,45; 50,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50,45; 52,22</t>
+          <t>50,53; 52,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50,58; 51,6</t>
+          <t>50,64; 51,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49,58; 50,7</t>
+          <t>49,57; 50,67</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51,5; 53,48</t>
+          <t>51,45; 53,51</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>50,66; 52,25</t>
+          <t>50,69; 52,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>50,06; 51,77</t>
+          <t>50,05; 51,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51,16; 52,75</t>
+          <t>51,29; 52,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50,87; 52,33</t>
+          <t>50,89; 52,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>48,82; 50,66</t>
+          <t>48,8; 50,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,49; 48,65</t>
+          <t>46,59; 48,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,56; 49,59</t>
+          <t>47,67; 49,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>48,83; 50,14</t>
+          <t>48,83; 50,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>50,01; 51,21</t>
+          <t>50,06; 51,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48,63; 49,95</t>
+          <t>48,61; 49,98</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49,63; 50,96</t>
+          <t>49,69; 50,98</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,09; 51,07</t>
+          <t>50,05; 51,01</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>49,74; 51,74</t>
+          <t>49,73; 51,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50,02; 52,15</t>
+          <t>49,97; 52,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51,17; 52,97</t>
+          <t>51,2; 52,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50,96; 52,31</t>
+          <t>50,87; 52,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>48,79; 50,7</t>
+          <t>48,58; 50,7</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>46,62; 48,92</t>
+          <t>46,58; 48,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47,48; 49,69</t>
+          <t>47,43; 49,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>45,92; 50,22</t>
+          <t>45,85; 50,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49,5; 50,94</t>
+          <t>49,48; 50,91</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>48,55; 50,17</t>
+          <t>48,58; 50,13</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49,6; 51,09</t>
+          <t>49,59; 51,06</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>46,99; 50,9</t>
+          <t>46,97; 50,89</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>49,33; 51,94</t>
+          <t>49,23; 51,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>47,88; 50,83</t>
+          <t>47,8; 50,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49,44; 51,65</t>
+          <t>49,43; 51,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49,59; 51,38</t>
+          <t>49,67; 51,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>49,11; 51,52</t>
+          <t>49,13; 51,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,6; 47,04</t>
+          <t>44,68; 47,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,21; 49,13</t>
+          <t>46,23; 48,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>46,58; 48,19</t>
+          <t>46,55; 48,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>49,61; 51,38</t>
+          <t>49,57; 51,36</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46,32; 48,19</t>
+          <t>46,27; 48,09</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47,86; 49,82</t>
+          <t>47,79; 49,77</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>48,07; 49,25</t>
+          <t>48,05; 49,2</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>52,31; 52,8</t>
+          <t>52,27; 52,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>51,75; 52,32</t>
+          <t>51,78; 52,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52,17; 52,7</t>
+          <t>52,16; 52,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52,48; 53,31</t>
+          <t>52,48; 53,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>50,47; 51,07</t>
+          <t>50,45; 51,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,86; 49,56</t>
+          <t>48,88; 49,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,31; 50,93</t>
+          <t>50,27; 50,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>49,39; 50,96</t>
+          <t>49,35; 50,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>51,45; 51,86</t>
+          <t>51,47; 51,82</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50,4; 50,84</t>
+          <t>50,38; 50,83</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51,3; 51,71</t>
+          <t>51,32; 51,71</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>50,98; 51,99</t>
+          <t>50,88; 52,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/MCS12_SP-Edad-trans_orig.xlsx
+++ b/data/trans_orig/MCS12_SP-Edad-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55,34</t>
+          <t>55,04</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>52,53</t>
+          <t>52,64</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>54,11</t>
+          <t>53,92</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53,68; 54,6</t>
+          <t>53,69; 54,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53,5; 54,58</t>
+          <t>53,49; 54,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53,84; 54,94</t>
+          <t>53,85; 54,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54,18; 56,04</t>
+          <t>53,87; 55,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>51,98; 53,19</t>
+          <t>51,88; 53,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,75; 53,3</t>
+          <t>51,71; 53,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,74; 54,0</t>
+          <t>52,78; 54,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>50,91; 53,72</t>
+          <t>51,15; 53,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53,01; 53,75</t>
+          <t>53,0; 53,79</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52,86; 53,78</t>
+          <t>52,86; 53,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53,55; 54,37</t>
+          <t>53,58; 54,37</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,17; 54,86</t>
+          <t>53,06; 54,65</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53,93</t>
+          <t>53,75</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>52,49</t>
+          <t>52,42</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>53,14</t>
+          <t>53,07</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>53,08; 53,94</t>
+          <t>53,07; 53,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52,54; 53,56</t>
+          <t>52,61; 53,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52,22; 53,42</t>
+          <t>52,28; 53,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52,75; 54,74</t>
+          <t>52,76; 54,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,5; 51,86</t>
+          <t>50,6; 51,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,63; 52,05</t>
+          <t>50,67; 52,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,96; 53,17</t>
+          <t>52,07; 53,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>51,54; 53,16</t>
+          <t>51,36; 53,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>52,1; 52,92</t>
+          <t>52,07; 52,86</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51,86; 52,7</t>
+          <t>51,84; 52,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52,34; 53,14</t>
+          <t>52,33; 53,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52,52; 53,74</t>
+          <t>52,43; 53,62</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52,97</t>
+          <t>53,1</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>52,46</t>
+          <t>52,29</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>52,71</t>
+          <t>52,7</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51,67; 52,85</t>
+          <t>51,7; 52,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51,31; 52,56</t>
+          <t>51,36; 52,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52,1; 53,17</t>
+          <t>52,07; 53,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52,13; 53,61</t>
+          <t>52,4; 53,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50,35; 51,52</t>
+          <t>50,39; 51,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,59; 50,21</t>
+          <t>48,69; 50,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,28; 52,53</t>
+          <t>51,3; 52,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51,9; 52,99</t>
+          <t>51,7; 52,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>51,19; 51,99</t>
+          <t>51,21; 52,01</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50,14; 51,17</t>
+          <t>50,15; 51,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51,8; 52,68</t>
+          <t>51,89; 52,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>52,2; 53,16</t>
+          <t>52,24; 53,12</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53,02</t>
+          <t>52,42</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>51,18</t>
+          <t>50,88</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>52,2</t>
+          <t>51,63</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>51,78; 53,04</t>
+          <t>51,74; 53,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51,0; 52,41</t>
+          <t>51,03; 52,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50,81; 52,23</t>
+          <t>50,88; 52,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52,01; 54,3</t>
+          <t>51,67; 53,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,0; 50,6</t>
+          <t>49,08; 50,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,72; 49,45</t>
+          <t>47,64; 49,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,45; 50,84</t>
+          <t>49,37; 50,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50,53; 52,27</t>
+          <t>50,31; 51,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50,64; 51,7</t>
+          <t>50,63; 51,61</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49,57; 50,67</t>
+          <t>49,57; 50,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50,32; 51,34</t>
+          <t>50,29; 51,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51,45; 53,51</t>
+          <t>51,22; 52,05</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51,63</t>
+          <t>51,71</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>49,51</t>
+          <t>49,39</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>50,58</t>
+          <t>50,54</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>50,69; 52,29</t>
+          <t>50,74; 52,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>50,05; 51,79</t>
+          <t>50,25; 51,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51,29; 52,79</t>
+          <t>51,26; 52,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50,89; 52,32</t>
+          <t>51,06; 52,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>48,8; 50,66</t>
+          <t>48,88; 50,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,59; 48,58</t>
+          <t>46,45; 48,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,67; 49,61</t>
+          <t>47,59; 49,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>48,83; 50,08</t>
+          <t>48,79; 50,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>50,06; 51,27</t>
+          <t>50,02; 51,2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48,61; 49,98</t>
+          <t>48,64; 49,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49,69; 50,98</t>
+          <t>49,66; 50,99</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,05; 51,01</t>
+          <t>50,07; 50,98</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51,66</t>
+          <t>51,71</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>48,04</t>
+          <t>49,77</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>49,4</t>
+          <t>50,7</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>49,73; 51,7</t>
+          <t>49,7; 51,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49,97; 52,17</t>
+          <t>50,0; 52,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51,2; 52,99</t>
+          <t>51,21; 52,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50,87; 52,24</t>
+          <t>50,99; 52,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>48,58; 50,7</t>
+          <t>48,64; 50,7</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>46,58; 48,84</t>
+          <t>46,68; 49,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47,43; 49,74</t>
+          <t>47,54; 49,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>45,85; 50,22</t>
+          <t>49,05; 50,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49,48; 50,91</t>
+          <t>49,48; 50,84</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>48,58; 50,13</t>
+          <t>48,52; 50,12</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49,59; 51,06</t>
+          <t>49,59; 51,01</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>46,97; 50,89</t>
+          <t>50,15; 51,15</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50,53</t>
+          <t>50,39</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>47,37</t>
+          <t>47,29</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>48,64</t>
+          <t>48,54</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>49,23; 51,93</t>
+          <t>49,22; 51,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>47,8; 50,7</t>
+          <t>47,89; 50,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49,43; 51,63</t>
+          <t>49,45; 51,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49,67; 51,41</t>
+          <t>49,37; 51,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>49,13; 51,55</t>
+          <t>49,06; 51,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,68; 47,09</t>
+          <t>44,61; 47,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,23; 48,94</t>
+          <t>46,23; 49,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>46,55; 48,19</t>
+          <t>46,47; 48,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>49,57; 51,36</t>
+          <t>49,59; 51,34</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46,27; 48,09</t>
+          <t>46,16; 48,1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47,79; 49,77</t>
+          <t>47,88; 49,81</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>48,05; 49,2</t>
+          <t>47,94; 49,1</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>52,82</t>
+          <t>52,64</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>50,46</t>
+          <t>50,68</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>51,61</t>
+          <t>51,63</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>52,27; 52,77</t>
+          <t>52,29; 52,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>51,78; 52,36</t>
+          <t>51,7; 52,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52,16; 52,7</t>
+          <t>52,19; 52,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52,48; 53,32</t>
+          <t>52,35; 52,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>50,45; 51,07</t>
+          <t>50,46; 51,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,88; 49,57</t>
+          <t>48,86; 49,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,27; 50,92</t>
+          <t>50,27; 50,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>49,35; 50,95</t>
+          <t>50,39; 50,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>51,47; 51,82</t>
+          <t>51,46; 51,85</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50,38; 50,83</t>
+          <t>50,39; 50,83</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51,32; 51,71</t>
+          <t>51,28; 51,71</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>50,88; 52,0</t>
+          <t>51,43; 51,83</t>
         </is>
       </c>
     </row>
